--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0046.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0046.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tôi cần thêm thời gian để quyết định…</t>
+          <t>Tôi cần thêm thời gian để suy nghĩ...</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Shocked</t>
+          <t>Bị sốc điện</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Tôi xin phép từ chối…</t>
+          <t>Tôi từ chối…</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hug</t>
+          <t>Ôm</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Đang thiết lập liên kết với Lightborne Horizons…</t>
+          <t>Đang kết nối với Lightborne Horizons…</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Tôi xin phép từ chối…</t>
+          <t>Tôi từ chối…</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>…Ready—</t>
+          <t>…Sẵn sàng—</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Để xem nào… Tôi sẽ đổi tên file, thêm vị trí và ngày tháng, rồi viết chú thích nhanh…</t>
+          <t>Để xem nào... ta chỉ cần đổi tên file, thêm vị trí với ngày tháng, rồi viết chú thích nhanh thôi...</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Kiểm tra quyền ảnh đại diện, chọn "Time Capsule Delivery" và gắn thẻ chủ đề sự kiện…</t>
+          <t>Kiểm tra quyền chân dung, chọn "Gửi Hộp Thời Gian", rồi gắn thẻ chủ đề sự kiện…</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Còn những phần quà thêm tôi chuẩn bị—</t>
+          <t>Còn về những món quà phụ ta chuẩn bị—</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đáng thử mà…</t>
+          <t>Thử cũng không sao...</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Tôi mới đến đây, vẫn đang cố tìm hiểu mọi thứ…</t>
+          <t>Mình mới đến đây, vẫn đang cố tìm hiểu mọi thứ...</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>T-Tôi có thể không giúp được nhiều…</t>
+          <t>T-Tôi có lẽ không giúp được nhiều đâu…</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>So I…</t>
+          <t>Vậy là...</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Màu hồng hoa hồng, hết hàng… Champagne, hết hàng…</t>
+          <t>Màu hồng hoa hồng, hết hàng... Champagne, hết hàng...</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Xin lỗi, tôi không thực sự hứng—</t>
+          <t>Xin lỗi, tớ không thực sự hứng thú—</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Nhà Thơ Vinh Dự của Ragunna, The Laureate của Septimont…</t>
+          <t>Nhà Vô Địch xứ Ragunna, Nhà Vô Địch của Septimont…</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Thành thật mà nói, tôi không biết mình muốn trở thành người như thế nào…</t>
+          <t>Thật lòng mà nói, mình cũng không biết mình muốn trở thành người như thế nào...</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Cậu nói đúng…</t>
+          <t>Đúng vậy…</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Về ngoại hình… tôi không nghĩ mình sẽ thay đổi nhiều…</t>
+          <t>Về ngoại hình... chắc mình không thay đổi nhiều đâu...</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đ-đừng nói ra chứ…</t>
+          <t>Ê ê, đừng có nói ra chứ…</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Tôi nghĩ mình sắp xong việc ở khu mua sắm rồi…</t>
+          <t>Ta nghĩ ta sắp xong việc ở trung tâm mua sắm rồi…</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>À… hóa ra tôi đi ngược hướng dòng chảy…</t>
+          <t>À… thì ra tao đã đi ngược dòng chảy…</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>(Khoảnh khắc khiến bạn chậm lại…)</t>
+          <t>("Một khoảnh khắc khiến mày phải chậm lại...")</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Tôi luôn nghĩ tính cách của cậu phù hợp với ngành Kỹ thuật hơn…</t>
+          <t>Tao cứ nghĩ tính cách của mày hợp với ngành Kỹ thuật hơn…</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>T-tôi biết…</t>
+          <t>T-Tôi biết mà...</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>(Hơi ngượng ngùng) Ugh, cậu thật là…</t>
+          <t>(Hơi ngượng ngùng) Ôi, cậu thật là... không chịu được!</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Xin lỗi…</t>
+          <t>Xin thứ lỗi…</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Miễn là Người Hướng Dẫn đồng ý…</t>
+          <t>Chừng nào Người Hướng Dẫn đồng ý…</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Miễn là Người Hướng Dẫn đồng ý…</t>
+          <t>Chừng nào Người Hướng Dẫn đồng ý…</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>(Gasp)</t>
+          <t>(Thở hổn hển)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>(Lặng lẽ ngưỡng mộ)</t>
+          <t>Lặng lẽ ngắm nhìn nó.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Ảnh</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tick tack, tick tack—</t>
+          <t>Tíc tắc, tíc tắc—</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cót két—Tíc tắc—Thình thịch, thình thịch, THÌNH…</t>
+          <t>Kẽo kẹt—Tích tắc—Tiếng đập, đập, ĐẬP...</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Trong khoảnh khắc đó, bạn chợt hiểu ra—</t>
+          <t>Khoảnh khắc ấy, cậu chợt hiểu ra—</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Không, lẽ ra không được như thế này… Giá như… tôi có thể…</t>
+          <t>Không, lẽ ra không được như thế này... Giá như... ta có thể...</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Không sao đâu… Tôi chỉ cần cẩn thận… Không để nó phát hiện ra tôi…</t>
+          <t>Không sao... Chỉ cần cẩn thận thôi... Không được để nó phát hiện ra mình...</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Nếu nó không bắt được tôi… T-tôi vẫn có thể thoát ra được…</t>
+          <t>Nếu nó không bắt được tớ... T-Tớ vẫn có thể thoát ra được...</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tôi phải… tiếp tục chạy… Nếu đến được đích… có lẽ tôi có thể…</t>
+          <t>Ta phải... tiếp tục chạy... Nếu đến được đích... có lẽ ta có thể...</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Creak— THUMP—</t>
+          <t>Kẽo kẹt— BỤP—</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Creak— THUMP— Creak—</t>
+          <t>Kẽo kẹt— BỤP— Kẽo kẹt—</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Obviously, it's—</t>
+          <t>Rõ ràng là—</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>(Cô ấy nghiêm túc một cách đáng ngạc nhiên khi nói đến chuyện này…)</t>
+          <t>Cô ấy lại nghiêm túc một cách bất ngờ khi nói đến chuyện này…</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Không, không phải thế… Đây không phải món quà của tôi…</t>
+          <t>Không, không phải thế... Đây không phải năng lực của ta...</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Bạn đã rất gần rồi…</t>
+          <t>Gần rồi đấy…</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Có vẻ như… bạn đang hiểu tôi hơn rồi đấy…</t>
+          <t>Có vẻ như... cậu đã hiểu ta hơn rồi đấy...</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Không, không phải thế… Đây không phải món quà của tôi…</t>
+          <t>Không, không phải thế... Đây không phải năng lực của ta...</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Bạn đã rất gần rồi…</t>
+          <t>Gần rồi đấy…</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Shion, đừng tự dọa mình—</t>
+          <t>Shion, đừng tự dọa mình chứ—</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Shion, you…</t>
+          <t>Shion, cậu…</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Trong lớp học vô tận này… hãy giúp tôi thu thập ba thứ chứa đựng tình cảm của tôi—</t>
+          <t>Trong lớp học bất tận này… hãy giúp ta thu thập ba thứ chứa đựng cảm xúc của ta—</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>(Có vẻ lần này cô ấy không quên gì cả…)</t>
+          <t>Có vẻ lần này cô ấy không quên gì cả…</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cậu ấy nói, cậu ấy rơi xuống từ những vì sao…</t>
+          <t>Hắn nói hắn rơi xuống từ những vì sao…</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>*Thở dài* Hôm qua tôi vừa mới dọn dẹp xong nơi này mà…</t>
+          <t>*Thở dài* Ta vừa dọn dẹp xong nơi này ngày hôm qua mà...</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Yip—</t>
+          <t>Ư—</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Gâu gâu—</t>
+          <t>Ư ư—</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>(Comfort her)</t>
+          <t>(An ủi cô ấy)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Nhưng thật tiếc khi tôi không thể tham dự lễ tiễn别 Professor Edgar…</t>
+          <t>Nhưng thật tiếc khi tôi không thể tham dự lễ tiễn biệt Professor Edgar…</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Để tôi giải thích rõ cho cậu—</t>
+          <t>Được rồi, để tôi giải thích cho cậu rõ—</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Tôi thấy mặt đất xanh kia rồi—</t>
+          <t>Ta thấy vùng đất xanh kia rồi—</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Bậc thầy ngôn ngữ, đến lượt cậu rồi—</t>
+          <t>Đến lượt cậu rồi, Bậc Thầy Ngôn Ngữ—</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -14294,8 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>************************
-NAME_TITLE_0024140::*******</t>
+          <t>************************</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14575,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14645,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14995,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -16535,8 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>***********************************
-```</t>
+          <t>***********************************</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16606,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>**************************************************************</t>
+          <t>*************************************************************</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16746,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>**********************************************************************</t>
+          <t>*********************************************************************</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16816,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>*******************************************************************************</t>
+          <t>******************************************************************************</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16956,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>**********************************************************</t>
+          <t>*********************************************************</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17096,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17236,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>********************************************************</t>
+          <t>*******************************************************</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17376,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>**************************</t>
+          <t>*************************</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17446,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>***********************************************</t>
+          <t>**********************************************</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17516,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>*********************************************************</t>
+          <t>********************************************************</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17656,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>***********************************************************</t>
+          <t>**********************************************************</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17796,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>**************************************************</t>
+          <t>*************************************************</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17936,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>*******************************************************************************</t>
+          <t>******************************************************************************</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18006,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>**************************************************************</t>
+          <t>*************************************************************</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18076,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>************************************************************************************</t>
+          <t>***********************************************************************************</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18216,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>*****************************************************</t>
+          <t>****************************************************</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18356,8 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>******************************************************
-```</t>
+          <t>******************************************************</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19407,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>*******</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19687,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20527,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>*******</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21437,8 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>****************************************************************
-NAME_TITLE_00242242:::******************************************************</t>
+          <t>****************************************************************</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21718,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21928,8 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>*****************************
-```</t>
+          <t>*****************************</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22279,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22769,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22979,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>*******</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23189,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23749,8 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>*****************
-```</t>
+          <t>*****************</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -24520,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24940,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25010,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25570,8 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>*************************************************************
-```</t>
+          <t>*************************************************************</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -26481,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26621,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>******</t>
+          <t>*******</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26971,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>*******</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27041,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27111,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27321,8 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>***************************************************
-```</t>
+          <t>***************************************************</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27882,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28582,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>*********</t>
+          <t>* * * * * * * * *</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28792,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -29142,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29212,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*********************************************************************</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29282,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>******************************************************</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29352,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>***************************************************************************************</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29422,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*************************************************************************************</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29492,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**************************************************</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29562,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>***************************************************************************</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29632,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*******************************************************</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29702,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>****************************************</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29772,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**********************************************************</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29842,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>******************************</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29912,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**********************************************************</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29982,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*****************************************************************************************</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30052,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*************************************************</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30122,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>****************************</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30192,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>***********************************</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30262,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>******************************************************************************</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30332,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30402,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>************************************************************************************</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30472,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**************************</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30612,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30682,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>***********************************************</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30752,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*****************************</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30822,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>*************</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30892,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**********************************</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30962,8 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>*
-```</t>
+          <t>**************************************************************************************</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31383,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -32783,8 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>******
-```</t>
+          <t>*******</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -33204,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>:********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33274,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>*********</t>
+          <t>* * * * * * * * *</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33484,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33694,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -34604,8 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>***************************
-```</t>
+          <t>***************************</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34745,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -35165,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>*********</t>
+          <t>* * * * * * * * *</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
